--- a/SaudiLeagueU21.xlsx
+++ b/SaudiLeagueU21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvarolopezmolina/Desktop/alnassracademy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3A7E71C-8352-6D4F-B43A-F3D72175CD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2502795-89A9-8F49-8B8C-7C22E45C84D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
